--- a/docs/evidence/cruise-fullflow-acceptance-20261024/公共切舱-manifest.xlsx
+++ b/docs/evidence/cruise-fullflow-acceptance-20261024/公共切舱-manifest.xlsx
@@ -78,7 +78,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEST0</t>
+          <t xml:space="preserve">MING</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -123,7 +123,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姓名</t>
+          <t xml:space="preserve">已齐</t>
         </is>
       </c>
     </row>
@@ -135,7 +135,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEST1</t>
+          <t xml:space="preserve">FANG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姓名</t>
+          <t xml:space="preserve">已齐</t>
         </is>
       </c>
     </row>
